--- a/data/S1972_73_FINAL.xlsx
+++ b/data/S1972_73_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -20402,7 +20420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20473,6 +20491,74 @@
       <c r="D3" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0012</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0012 'Kval o novou ČNHL' (L25, parent=NODE_S1972_73_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0020</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0020 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1972_73_0013) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0024</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0024 'KVAL  skupina A' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0025</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0025 'KVAL  skupina B' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -58465,6 +58551,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0012</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1972_73_0012 'Kval o novou ČNHL' (L25, parent=NODE_S1972_73_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0020</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1972_73_0020 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1972_73_0013) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0024</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1972_73_0024 'KVAL  skupina A' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0025</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1972_73_0025 'KVAL  skupina B' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1972_73_FINAL.xlsx
+++ b/data/S1972_73_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20420,7 +20420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20495,14 +20495,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1972_73_0012</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0012 'Kval o novou ČNHL' (L25, parent=NODE_S1972_73_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20512,14 +20507,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1972_73_0020</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0020 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1972_73_0013) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20529,14 +20519,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1972_73_0024</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0024 'KVAL  skupina A' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20546,17 +20531,384 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1972_73_0025</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1972_73_0025 'KVAL  skupina B' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Horní Lom' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tisová' → 'Heřmanův Městec' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chotěvice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -27825,12 +28177,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -28119,12 +28471,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -28329,12 +28681,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -28722,12 +29074,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Slezan Opava</t>
         </is>
       </c>
     </row>
@@ -29404,12 +29756,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -29908,12 +30260,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem.</t>
+          <t>Rožmitál pod Třemšínem = Spartak Rožmitál (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Pribram). Patterns: Spartak -&gt; VK Rožmitál. city Rožmitál pod Třemšínem. || TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Rožmitál</t>
+          <t>Rožmitál pod Třemšínem</t>
         </is>
       </c>
     </row>
@@ -30081,12 +30433,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -30338,12 +30690,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -30716,12 +31068,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -30805,12 +31157,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -32656,12 +33008,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha.</t>
+          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha. || TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>VS Technika</t>
         </is>
       </c>
     </row>
@@ -33024,12 +33376,12 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -33721,12 +34073,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou.</t>
+          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou. || TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Týnec nad Sázavou</t>
+          <t>Týnec nad Labem</t>
         </is>
       </c>
     </row>
@@ -34952,12 +35304,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín.</t>
+          <t>Kolín = SC Marimex Kolín (Wiki D42 - registr ustavy 04/2026). Genealogie: Sparta Kolín -&gt; Spartak Tatra Kolín (50.leta - Tatra Kolín = podnik) -&gt; Dukla Kolín (vojensky) -&gt; SK Kolín -&gt; SC Marimex Kolín. KOL = okres Kolín. city Kolín. || Starý Kolín = Jiskra Kara Starý Kolín (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Kolín). Kara = podnik. city Starý Kolín. || TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>Kara Starý Kolín</t>
+          <t>Kolín</t>
         </is>
       </c>
     </row>
@@ -37004,12 +37356,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -37978,12 +38330,12 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Cesky Krumlov). 'Sm.' = zkratka Smrcina. city Horní Planá. || TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>Sm. Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -38886,12 +39238,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou.</t>
+          <t>Stranná u Kamenice nL Lipou = TJ Sokol Stranná (Wiki D42 - registr ustavy 04/2026). Vysocina/Pelhrimovsky kraj. POZOR: hraninicni region s Jihocesko - prerodu uzemi. city Stranná u Kamenice nad Lipou. || TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Stranná u Kamenice nad Lipou</t>
+          <t>Kamenice nad Lipou</t>
         </is>
       </c>
     </row>
@@ -40036,12 +40388,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -41973,12 +42325,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Horní Lom' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Horní Lom</t>
         </is>
       </c>
     </row>
@@ -44002,12 +44354,12 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -46607,12 +46959,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Tisová = TJ Banik Tisová (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Sokolov). Hornicka obec u Sokolova. POZOR: NE Tisova u Mostu (Severocesky). city Tisová.</t>
+          <t>Tisová = TJ Banik Tisová (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Sokolov). Hornicka obec u Sokolova. POZOR: NE Tisova u Mostu (Severocesky). city Tisová. || TBD: city 'Tisová' → 'Heřmanův Městec' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Tisová</t>
+          <t>Heřmanův Městec</t>
         </is>
       </c>
     </row>
@@ -46649,12 +47001,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka.</t>
+          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka. || TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Nová Paka</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
@@ -46775,12 +47127,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Chotěvice = TJ Sokol Chotěvice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov). city Chotěvice.</t>
+          <t>Chotěvice = TJ Sokol Chotěvice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov). city Chotěvice. || TBD: city 'Chotěvice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>Chotěvice</t>
+          <t>Lomnice nad Popelkou</t>
         </is>
       </c>
     </row>
@@ -47079,12 +47431,12 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>Žďár nad Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (vyrobce kovacich/lisovacich strojů). Patterns: Tatran -&gt; Spartak -&gt; ŽĎAS Žďár nL Sázavou. city Žďár nad Sázavou.</t>
+          <t>Žďár nad Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (vyrobce kovacich/lisovacich strojů). Patterns: Tatran -&gt; Spartak -&gt; ŽĎAS Žďár nL Sázavou. city Žďár nad Sázavou. || TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -47121,12 +47473,12 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí.</t>
+          <t>Velké Meziříčí = TJ Kablo Velké Meziříčí (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihomoravsky kraj. **Kablo** = kabelovy podnik (pobocka). city Velké Meziříčí. || TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>Kablo Velké Meziříčí</t>
+          <t>Velké Meziříčí</t>
         </is>
       </c>
     </row>
@@ -48280,12 +48632,12 @@
       </c>
       <c r="I476" t="inlineStr">
         <is>
-          <t>Žďár nad Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (vyrobce kovacich/lisovacich strojů). Patterns: Tatran -&gt; Spartak -&gt; ŽĎAS Žďár nL Sázavou. city Žďár nad Sázavou.</t>
+          <t>Žďár nad Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (vyrobce kovacich/lisovacich strojů). Patterns: Tatran -&gt; Spartak -&gt; ŽĎAS Žďár nL Sázavou. city Žďár nad Sázavou. || TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>Praha</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -49291,12 +49643,12 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>Bystřice</t>
+          <t>Bystřice pod Hostýnem</t>
         </is>
       </c>
     </row>
@@ -50510,12 +50862,12 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>Bystřice</t>
+          <t>Bystřice pod Hostýnem</t>
         </is>
       </c>
     </row>
@@ -50809,12 +51161,12 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -53164,12 +53516,12 @@
       </c>
       <c r="I588" t="inlineStr">
         <is>
-          <t>Vyšné Opátske = TJ Pokrok Vyšné Opátske (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj (okres Sabinov). 'Opátske' bez diakritiky. NE Vysné Opátske mestska cast Kosic! city Vyšné Opátske.</t>
+          <t>Vyšné Opátske = TJ Pokrok Vyšné Opátske (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj (okres Sabinov). 'Opátske' bez diakritiky. NE Vysné Opátske mestska cast Kosic! city Vyšné Opátske. || TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J588" t="inlineStr">
         <is>
-          <t>Pokrok Vyšné Opátske</t>
+          <t>Vyšné Opátske</t>
         </is>
       </c>
     </row>
@@ -58557,11 +58909,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -58606,21 +58958,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1972_73_0012</t>
+          <t>CLUB_S1972_73_0010</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1972_73_0012 'Kval o novou ČNHL' (L25, parent=NODE_S1972_73_0003) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -58628,21 +58978,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1972_73_0020</t>
+          <t>CLUB_S1972_73_0017</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1972_73_0020 'Kvalifikace o I.ČNHL' (L25, parent=NODE_S1972_73_0013) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -58650,21 +58998,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1972_73_0024</t>
+          <t>CLUB_S1972_73_0022</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1972_73_0024 'KVAL  skupina A' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -58672,24 +59018,642 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1972_73_0025</t>
+          <t>CLUB_S1972_73_0031</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1972_73_0025 'KVAL  skupina B' (L35, parent=NODE_S1972_73_0023) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0047</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0059</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0063</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0069</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0078</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0080</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0088</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0094</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0131</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0140</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0156</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0184</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0230</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0252</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0266</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0271</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0296</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0342</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Teplice' → 'Horní Lom' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0389</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0443</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0444</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tisová' → 'Heřmanův Městec' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0445</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0448</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chotěvice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0455</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0456</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0484</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0487</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0507</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0535</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0543</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1972_73_0598</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -65902,6 +66866,11 @@
           <t>CLUB_S1971_72_0120</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>TR_S1972_73_00151</t>
@@ -81854,6 +82823,11 @@
           <t>CLUB_S1971_72_0316</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V41" t="inlineStr">
         <is>
           <t>TR_S1972_73_00281</t>
@@ -81899,6 +82873,11 @@
       <c r="R42" t="inlineStr">
         <is>
           <t>CLUB_S1971_72_0327</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>zanik</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">

--- a/data/S1972_73_FINAL.xlsx
+++ b/data/S1972_73_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20420,7 +20420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20497,7 +20497,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -20509,7 +20509,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20521,7 +20521,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20533,7 +20533,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20545,7 +20545,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20557,7 +20557,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20569,7 +20569,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20581,7 +20581,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20593,7 +20593,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20605,7 +20605,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20617,7 +20617,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20629,7 +20629,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20641,7 +20641,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20653,7 +20653,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20665,7 +20665,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20677,7 +20677,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20689,7 +20689,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20701,214 +20701,10 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Teplice' → 'Horní Lom' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tisová' → 'Heřmanův Městec' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chotěvice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -20925,7 +20721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:L119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20984,6 +20780,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -21026,6 +20827,11 @@
           <t>10 týmů, čtyřkolově + playoff (top 4: SF na 3 výhry, finále na 4). Mistr: Tesla Pardubice. Sestup: Motor ČB.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21073,6 +20879,11 @@
           <t>Vítězové 4 skupin II.ligy. Dvoukolově. Top 2 do I.ligy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -21115,6 +20926,11 @@
           <t>I.ČNHL: sk. A + B; 1.SNHL → finále + o udržení. Prolínací o I.ligu. Kval o novou ČNHL.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -21157,6 +20973,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -21199,6 +21020,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -21241,6 +21067,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -21283,6 +21114,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -21325,6 +21161,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -21535,6 +21376,11 @@
           <t>Divize: 6 skupin CZ (A-F) + 2 skupiny SVK + kvalifikace o I.ČNHL.</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0014</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -21577,6 +21423,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -21619,6 +21470,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0016</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -21661,6 +21517,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0017</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -21703,6 +21564,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0018</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -21745,6 +21611,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0019</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -21787,6 +21658,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0020</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -21876,6 +21752,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0024</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -21918,6 +21799,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21965,6 +21851,11 @@
           <t>PDF používá termín „Kvalifikace o divizi“, XLS/prepared „Kvalifikace o postup do divize“; sjednoceno na Kvalifikace o divizi.</t>
         </is>
       </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0026</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -22007,6 +21898,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0027</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -22049,6 +21945,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0028</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -22091,6 +21992,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0029</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -22427,6 +22333,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0033</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -22469,6 +22380,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0034</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -22978,6 +22894,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0049</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -23020,6 +22941,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0050</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -23193,6 +23119,11 @@
           <t>Kvalifikace o I.A třídu</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0055</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -23319,6 +23250,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0058</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -23361,6 +23297,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0059</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -23403,6 +23344,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0060</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -23445,6 +23391,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0061</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -23487,6 +23438,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0062</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -23529,6 +23485,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0063</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -23571,6 +23532,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0064</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -23613,6 +23579,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0065</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -23655,6 +23626,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0066</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -23697,6 +23673,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0067</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -23791,6 +23772,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0068</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -23833,6 +23819,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0069</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -23875,6 +23866,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0070</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -23959,6 +23955,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0072</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -24001,6 +24002,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0073</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -24043,6 +24049,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0074</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -24085,6 +24096,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0075</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -24132,6 +24148,11 @@
           <t>kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0076</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -24174,6 +24195,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0079</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -24216,6 +24242,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0080</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -24258,6 +24289,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0081</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -24300,6 +24336,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0082</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -24342,6 +24383,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0083</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -24384,6 +24430,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0084</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -24426,6 +24477,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0085</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -24468,6 +24524,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0086</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -24510,6 +24571,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0087</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -24557,6 +24623,11 @@
           <t>Kvalifikace o postup do krajského přeboru</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0088</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -24604,6 +24675,11 @@
           <t>kvalifikace</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0089</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -24646,6 +24722,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0090</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -24688,6 +24769,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0091</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -24730,6 +24816,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0092</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -24772,6 +24863,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0093</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -24814,6 +24910,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0094</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -24856,6 +24957,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0095</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -24982,6 +25088,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0096</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -25024,6 +25135,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0097</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -25066,6 +25182,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0098</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -25108,6 +25229,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0099</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -25150,6 +25276,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0100</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -25239,6 +25370,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0096</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -25281,6 +25417,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0097</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -25370,6 +25511,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0101</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -25454,6 +25600,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0103</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -25496,6 +25647,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0104</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -25889,6 +26045,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0116</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -25931,6 +26092,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0117</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -25973,6 +26139,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0118</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -26013,6 +26184,11 @@
       <c r="J119" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>NODE_S1971_72_0119</t>
         </is>
       </c>
     </row>
@@ -28177,12 +28353,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -28471,12 +28647,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -28681,12 +28857,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -29074,12 +29250,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice. || TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Slavoj České Budějovice B (Wiki D42 - registr ustavy 04/2026). B-tym hlavni Motor CB chain. city České Budějovice.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Slezan Opava</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -29756,12 +29932,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -31068,12 +31244,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -33008,12 +33184,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha. || TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Praha = TJ VS Technika Praha (Wiki D42 - registr ustavy 04/2026). **VS Technika** = Vysokoskolsky sport Technika (CVUT Praha studentsky klub). city Praha.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>VS Technika</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34073,12 +34249,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou. || TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Týnec = TJ Metaz Týnec (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (Týnec nad Sázavou, okres Benesov). **Metaz** = strojírenský podnik (slévárna). city Týnec nad Sázavou.</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>Týnec nad Labem</t>
+          <t>Týnec nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -40388,12 +40564,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -42325,12 +42501,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice. || TBD: city 'Teplice' → 'Horní Lom' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Oprava city: „Testroj Teplice" → „Teplice" (Testroj = závod). || Sokol Testroj Teplice 52/53 - hlavni klub (Testroj podnik). Teplice = HC Stadion Teplice (Wiki D42 - registr 04/2026). Genealogie: Technomat Teplice (49/50, podnik Technomat) -&gt; Sokol Testroj Teplice (52/53, Testroj/Somet podnik) -&gt; Tatran Teplice (53/54+ DSO reforma). Plus Sklarny Retenice paralelni klub (skladlo se 55/56 s Tatranem Teplice). Dnesni klub HC Stadion Teplice. Patterns: Technomat Teplice, Sokol Testroj, Tatran Teplice, Sklárny Řetenice. city Teplice. || Sokol Testroj Teplice 52/53 (20_Ústecký okresni). Testroj = podnik (puvodne Technomat). Teplice = HC Stadion Teplice / HC Teplice Huskies (Wiki D42 + hokej.cz - 04/2026). Genealogie: Klub zalozen 1945. Technomat Teplice (1949-50, podnikovy klub Technomat) -&gt; Sokol Testroj (1952) -&gt; Tatran Teplice (1953+, DSO reforma) -&gt;... -&gt; HC Stadion Teplice (do 2007, klub rozpusten po sestupu kvuli neprovozuschopnosti ZS) -&gt; HC Teplice Huskies (2018+ novy mladeznicky klub, novy zimni stadion otevren 2019). city Teplice. POZOR: Teplice nad Metují = JINE MESTO (Královehradecky kraj, Slavoj Teplice nL Metují) - separate od stredoceskych Teplic. || Teplice = HC Stadion Teplice (1945-2007) -&gt; HC Teplice Huskies (2019-dnes) (Pavlovo upresneni 04/2026 + Wiki + FK Teplice paralelni vyvoj). Genealogie podle paralelni fotbalove linie: 1945 zalozeni -&gt; 1948 Sokol -&gt; 1949 Technomat (podnik OD - obchodni dum) -&gt; 1951 Vodotechna (vodni stavby) -&gt; 1952 Ingstav (inzenyrska stavba) -&gt; 1953 Tatran Teplice (DSO reforma) -&gt; 1960 Slovan -&gt; 1966 Sklo Union -&gt; po 1991 menici se nazvy -&gt; 2007 PRERUSENI provozu - nositel hokejove tradice mesta pokracuje v Teplice Huskies (2019) -&gt; 2010 zbytky presun do Biliny -&gt; 2019 obnoveni HC Teplice Huskies (novy ZS). Patterns: Technomat Teplice, Vodotechna, Tatran Teplice, Slovan Teplice. Plus mensi paralelni kluby v 50. letech: Sokol Testroj/Somet/Ingstav, Sokol Sklarny Retenice, Jiskra Retenice (1955 sloucena s Tatranem), Spartak Trnovany, Banik Teplice, Lokomotiva Teplice, Tatran Sobedruhy. Retenice + Trnovany + Sobedruhy = mestske casti Teplic (Retenice oficialne od 1963). Sklarny Retenice = city Teplice. || Teplice (Wiki D42 - registr ustavy 04/2026). Hlavni chain HC Stadion Teplice (1945-2007) -&gt; Teplice Huskies (2019-): Technomat -&gt; Vodotechna -&gt; Ingstav -&gt; Tatran (1953) -&gt; Slovan (1960) -&gt; Sklo Union (1966). Plus mestske casti: Retenice (sklarny od 1890), Trnovany, Sobedruhy. city Teplice.</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>Horní Lom</t>
+          <t>Teplice</t>
         </is>
       </c>
     </row>
@@ -44354,12 +44530,12 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -46959,12 +47135,12 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>Tisová = TJ Banik Tisová (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Sokolov). Hornicka obec u Sokolova. POZOR: NE Tisova u Mostu (Severocesky). city Tisová. || TBD: city 'Tisová' → 'Heřmanův Městec' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Tisová = TJ Banik Tisová (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Sokolov). Hornicka obec u Sokolova. POZOR: NE Tisova u Mostu (Severocesky). city Tisová.</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>Heřmanův Městec</t>
+          <t>Tisová</t>
         </is>
       </c>
     </row>
@@ -47001,12 +47177,12 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka. || TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Nová Paka = Jiskra/Sokol Nová Paka (Wiki D42 - registr ustavy 04/2026). Vychodocesky kraj (okres Jicin). city Nová Paka.</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>Lomnice nad Popelkou</t>
+          <t>Nová Paka</t>
         </is>
       </c>
     </row>
@@ -47127,12 +47303,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>Chotěvice = TJ Sokol Chotěvice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov). city Chotěvice. || TBD: city 'Chotěvice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Chotěvice = TJ Sokol Chotěvice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Trutnov). city Chotěvice.</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>Lomnice nad Popelkou</t>
+          <t>Chotěvice</t>
         </is>
       </c>
     </row>
@@ -49643,12 +49819,12 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>Bystřice pod Hostýnem</t>
+          <t>Bystřice u Benešova</t>
         </is>
       </c>
     </row>
@@ -50862,12 +51038,12 @@
       </c>
       <c r="I526" t="inlineStr">
         <is>
-          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova. || TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Bystřice u Benešova = TJ Tatran Bystřice (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Benesov). Patterns: Sokol Bystřice -&gt; Tatran Bystřice. NE Bystřice nL Pernstejnem (Vysocina), NE Bystřice pod Hostýnem (Zlinsky), NE Bystřice nL Olší/Frýdek-Místek (Severomoravsky), NE Velká Bystřice (Olomouc). city Bystřice u Benešova.</t>
         </is>
       </c>
       <c r="J526" t="inlineStr">
         <is>
-          <t>Bystřice pod Hostýnem</t>
+          <t>Bystřice u Benešova</t>
         </is>
       </c>
     </row>
@@ -51161,12 +51337,12 @@
       </c>
       <c r="I533" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J533" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -58909,7 +59085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -58963,12 +59139,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0010</t>
+          <t>CLUB_S1972_73_0059</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58983,12 +59159,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0017</t>
+          <t>CLUB_S1972_73_0063</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59003,12 +59179,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0022</t>
+          <t>CLUB_S1972_73_0069</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59023,12 +59199,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0031</t>
+          <t>CLUB_S1972_73_0080</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'České Budějovice' → 'Slezan Opava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59043,12 +59219,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0047</t>
+          <t>CLUB_S1972_73_0088</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -59063,12 +59239,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0059</t>
+          <t>CLUB_S1972_73_0094</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -59083,12 +59259,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0063</t>
+          <t>CLUB_S1972_73_0140</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59103,12 +59279,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0069</t>
+          <t>CLUB_S1972_73_0184</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59123,12 +59299,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0078</t>
+          <t>CLUB_S1972_73_0230</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59143,12 +59319,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0080</t>
+          <t>CLUB_S1972_73_0252</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59163,12 +59339,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0088</t>
+          <t>CLUB_S1972_73_0266</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -59183,12 +59359,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0094</t>
+          <t>CLUB_S1972_73_0271</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59203,12 +59379,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0131</t>
+          <t>CLUB_S1972_73_0443</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Praha' → 'VS Technika' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -59223,12 +59399,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0140</t>
+          <t>CLUB_S1972_73_0455</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59243,12 +59419,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0156</t>
+          <t>CLUB_S1972_73_0456</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Týnec nad Sázavou' → 'Týnec nad Labem' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59263,12 +59439,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0184</t>
+          <t>CLUB_S1972_73_0484</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -59283,12 +59459,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0230</t>
+          <t>CLUB_S1972_73_0487</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -59303,357 +59479,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1972_73_0252</t>
+          <t>CLUB_S1972_73_0598</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0266</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0271</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0296</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0342</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Teplice' → 'Horní Lom' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0389</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0443</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0444</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Tisová' → 'Heřmanův Městec' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0445</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Nová Paka' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0448</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Chotěvice' → 'Lomnice nad Popelkou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0455</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0456</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0484</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0487</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0507</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0535</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Bystřice' → 'Bystřice pod Hostýnem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0543</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CLUB_S1972_73_0598</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F36"/>
+  <autoFilter ref="A1:F19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1972_73_FINAL.xlsx
+++ b/data/S1972_73_FINAL.xlsx
@@ -20721,7 +20721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L119"/>
+  <dimension ref="A1:N119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20783,6 +20783,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1972_73_FINAL.xlsx
+++ b/data/S1972_73_FINAL.xlsx
@@ -21067,6 +21067,16 @@
           <t>NODE_S1972_73_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21081,6 +21091,14 @@
         <is>
           <t>NODE_S1971_72_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -21114,6 +21132,8 @@
           <t>NODE_S1972_73_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21128,6 +21148,14 @@
         <is>
           <t>NODE_S1971_72_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -21161,6 +21189,8 @@
           <t>NODE_S1972_73_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21175,6 +21205,14 @@
         <is>
           <t>NODE_S1971_72_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21292,6 +21330,8 @@
           <t>NODE_S1972_73_0003</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21301,6 +21341,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -22207,6 +22255,8 @@
           <t>NODE_S1972_73_0026</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22216,6 +22266,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -22249,6 +22307,8 @@
           <t>NODE_S1972_73_0026</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22258,6 +22318,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -23072,6 +23140,8 @@
           <t>NODE_S1972_73_0048</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23081,6 +23151,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -23438,6 +23516,8 @@
           <t>NODE_S1972_73_0055</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23452,6 +23532,14 @@
         <is>
           <t>NODE_S1971_72_0062</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="61">
@@ -24383,6 +24471,8 @@
           <t>NODE_S1972_73_0075</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24397,6 +24487,14 @@
         <is>
           <t>NODE_S1971_72_0083</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -25004,6 +25102,12 @@
           <t>NODE_S1972_73_0086</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NODE_S1972_73_0093</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25013,6 +25117,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -25046,6 +25158,8 @@
           <t>NODE_S1972_73_0086</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25055,6 +25169,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">

--- a/data/S1972_73_FINAL.xlsx
+++ b/data/S1972_73_FINAL.xlsx
@@ -719,6 +719,11 @@
           <t>Tesla Pardubice</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>36</v>
       </c>
@@ -795,11 +800,6 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>Dukla Jihlava</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>M</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -20420,7 +20420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20707,6 +20707,13 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1972/73 první play-off: Tesla Pardubice (1. ZČ) ve finále porazila Duklu Jihlava 4:2 — první titul Pardubic. M badge opraven (byl chybně u Dukly). Doloženo webem.</t>
         </is>
       </c>
     </row>
@@ -21132,8 +21139,6 @@
           <t>NODE_S1972_73_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21189,8 +21194,6 @@
           <t>NODE_S1972_73_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21330,8 +21333,6 @@
           <t>NODE_S1972_73_0003</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22255,8 +22256,6 @@
           <t>NODE_S1972_73_0026</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22307,8 +22306,6 @@
           <t>NODE_S1972_73_0026</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23140,8 +23137,6 @@
           <t>NODE_S1972_73_0048</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23516,8 +23511,6 @@
           <t>NODE_S1972_73_0055</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24471,8 +24464,6 @@
           <t>NODE_S1972_73_0075</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25107,7 +25098,6 @@
           <t>NODE_S1972_73_0093</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25158,8 +25148,6 @@
           <t>NODE_S1972_73_0086</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -58963,7 +58951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59203,6 +59191,18 @@
       <c r="B20" t="inlineStr">
         <is>
           <t>Pro sezonu 1973/1974 vznikla 1. ČNHL (12 týmů) a 2. ČNHL (24 týmů ve 3 skupinách); přechodová logika převzata z PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tesla Pardubice</t>
         </is>
       </c>
     </row>

--- a/data/S1972_73_FINAL.xlsx
+++ b/data/S1972_73_FINAL.xlsx
@@ -20495,21 +20495,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1972/73 první play-off: Tesla Pardubice (1. ZČ) ve finále porazila Duklu Jihlava 4:2 — první titul Pardubic. M badge opraven (byl chybně u Dukly). Doloženo webem.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rožmitál' → 'Rožmitál pod Třemšínem' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -20521,7 +20516,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -20533,7 +20528,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -20545,7 +20540,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -20557,7 +20552,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -20569,7 +20564,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id oprava → CLUB_S1971_72_0435 (strong, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -20581,7 +20576,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -20593,7 +20588,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kara Starý Kolín' → 'Kolín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -20605,7 +20600,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -20617,7 +20612,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sm. Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -20629,7 +20624,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20641,7 +20636,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Stranná u Kamenice nad Lipou' → 'Kamenice nad Lipou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20653,7 +20648,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20665,7 +20660,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20677,7 +20672,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kablo Velké Meziříčí' → 'Velké Meziříčí' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20689,7 +20684,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Praha' → 'Žďár nad Sázavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20701,19 +20696,24 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Pokrok Vyšné Opátske' → 'Vyšné Opátske' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1972/73 první play-off: Tesla Pardubice (1. ZČ) ve finále porazila Duklu Jihlava 4:2 — první titul Pardubic. M badge opraven (byl chybně u Dukly). Doloženo webem.</t>
         </is>
       </c>
     </row>
